--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Chart with Filtering, Grouping, and Ordering_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Chart with Filtering, Grouping, and Ordering_report.xlsx
@@ -426,11 +426,11 @@
           <c:showLeaderLines val="0"/>
         </c:dLbls>
         <c:overlap val="100"/>
-        <c:axId val="1457403661"/>
         <c:axId val="526935498"/>
+        <c:axId val="1615081754"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1457403661"/>
+        <c:axId val="526935498"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -473,14 +473,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526935498"/>
+        <c:crossAx val="1615081754"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="526935498"/>
+        <c:axId val="1615081754"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -531,7 +531,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1457403661"/>
+        <c:crossAx val="526935498"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1160,7 +1160,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8aa146c6-5c47-4a76-b386-696ea698e02d}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{e046870b-234d-4131-a1ad-a60413458c11}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Chart with Filtering, Grouping, and Ordering_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Chart with Filtering, Grouping, and Ordering_report.xlsx
@@ -426,11 +426,11 @@
           <c:showLeaderLines val="0"/>
         </c:dLbls>
         <c:overlap val="100"/>
-        <c:axId val="526935498"/>
-        <c:axId val="1615081754"/>
+        <c:axId val="1797880418"/>
+        <c:axId val="18023371"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="526935498"/>
+        <c:axId val="1797880418"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -473,14 +473,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1615081754"/>
+        <c:crossAx val="18023371"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1615081754"/>
+        <c:axId val="18023371"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -531,7 +531,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526935498"/>
+        <c:crossAx val="1797880418"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1160,7 +1160,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{e046870b-234d-4131-a1ad-a60413458c11}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{bd1f0cb1-6dee-4fbc-9223-e2c16810f63c}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Chart with Filtering, Grouping, and Ordering_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Chart with Filtering, Grouping, and Ordering_report.xlsx
@@ -426,11 +426,11 @@
           <c:showLeaderLines val="0"/>
         </c:dLbls>
         <c:overlap val="100"/>
-        <c:axId val="1797880418"/>
         <c:axId val="18023371"/>
+        <c:axId val="1700675404"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1797880418"/>
+        <c:axId val="18023371"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -473,14 +473,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18023371"/>
+        <c:crossAx val="1700675404"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="18023371"/>
+        <c:axId val="1700675404"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -531,7 +531,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1797880418"/>
+        <c:crossAx val="18023371"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1160,7 +1160,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{bd1f0cb1-6dee-4fbc-9223-e2c16810f63c}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5b3d33ac-abd9-4c5d-a423-d24b588cd8bc}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
